--- a/advanced/ResNet.xlsx
+++ b/advanced/ResNet.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="78">
   <si>
     <t>Residual Network (ResNet)</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>Copyright (c) 2026 xyzln</t>
+  </si>
+  <si>
+    <t>This work is based on ai-by-hand-excel</t>
+  </si>
+  <si>
+    <t>&lt;https://github.com/ImagineAILab/ai-by-hand-excel&gt;,</t>
+  </si>
+  <si>
+    <t>Copyright (c) 2024 Tom Yeh, licensed under the MIT License.</t>
   </si>
   <si>
     <t>Permission is hereby granted, free of charge, to any person obtaining a copy</t>
@@ -8438,7 +8447,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="116.7109375" customWidth="1"/>
@@ -8476,22 +8485,22 @@
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="18" t="s">
-        <v>63</v>
-      </c>
+      <c r="A8" s="18"/>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="18" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="18"/>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="18" t="s">
@@ -8504,12 +8513,12 @@
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="18"/>
+      <c r="A14" s="18" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="18" t="s">
-        <v>68</v>
-      </c>
+      <c r="A15" s="18"/>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="18" t="s">
@@ -8522,23 +8531,41 @@
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="18" t="s">
-        <v>71</v>
-      </c>
+      <c r="A18" s="18"/>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="18" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="18" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
